--- a/nursing/フォーマット/06_事故苦情ヒヤリ様式/02_ヒヤリハット報告書.xlsx
+++ b/nursing/フォーマット/06_事故苦情ヒヤリ様式/02_ヒヤリハット報告書.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,31 +26,37 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00163A2B"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -62,21 +68,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D97706"/>
+        <fgColor rgb="00E4EFE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFFAFE"/>
+        <fgColor rgb="001F4D3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
+        <fgColor rgb="00F6EDDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -85,35 +91,60 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -477,154 +508,323 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ヒヤリハット報告書</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>「事故には至らなかったが、ヒヤリとした／ハッとした」事例を共有し、事故を未然に防ぐ</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>報告日 / 報告者</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
           <t>発生日時</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　　月　　日（　）　　時　　分</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>報告者氏名</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　年　　月　　日　　　時　　分頃</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>発生場所</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>当事者氏名（利用者）</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>ヒヤリハットの種類</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>転倒ヒヤリ ・ 誤薬ヒヤリ ・ 急変ヒヤリ ・ その他（　　　）</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>深刻度</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>①繰り返す可能性あり  ②重大事故に繋がる可能性あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>【発生した状況】（どのような状況でヒヤリハットが起きたか）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>例）服薬介助の際に、同日処方された2種類の薬のうち1種類の投与を失念しそうになった。利用者本人からの指摘で気づいた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>【なぜヒヤリとしたか・原因分析】</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>例）新しい薬が追加されたことを担当者間で共有できていなかった。薬の一覧表が最新版に更新されていなかった。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>【対応策・再発防止策】（具体的な対策と期限）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>例）①薬の一覧表を即日更新し、全担当者にメール共有。②今後の薬の変更は必ず記録簿に即日記入する運用に変更。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>報告日：　　年　　月　　日　　報告者署名：　　　　　　　　管理者確認：　　　　　　（　　年　　月　　日）</t>
-        </is>
-      </c>
+          <t>対象利用者（任意）</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="8" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>どんなことが起きたか（具体的に）</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="8" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>考えられる原因</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="8" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>今後の対策・気づき</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>危険度</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>□低　□中　□高（事故の可能性大）</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>カンファレンスでの共有</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>□済　□予定（　月　日）</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>※ 責任追及ではなく「情報共有・予防」が目的。気軽に・たくさん出すことが安全文化につながります。</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="A9:H9"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A10:H13"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="A16:H18"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A21:H23"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="C4:H4"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>